--- a/main/ig/StructureDefinition-FRLMSOPInstance.xlsx
+++ b/main/ig/StructureDefinition-FRLMSOPInstance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T14:19:44+00:00</t>
+    <t>2026-09-14T09:04:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-FRLMSOPInstance.xlsx
+++ b/main/ig/StructureDefinition-FRLMSOPInstance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T09:04:12+00:00</t>
+    <t>2026-09-23T09:36:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-FRLMSOPInstance.xlsx
+++ b/main/ig/StructureDefinition-FRLMSOPInstance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T09:36:17+00:00</t>
+    <t>2026-09-28T10:07:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-FRLMSOPInstance.xlsx
+++ b/main/ig/StructureDefinition-FRLMSOPInstance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-28T10:07:47+00:00</t>
+    <t>2026-09-30T20:10:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -286,7 +286,7 @@
     <t>UUID SOP instance</t>
   </si>
   <si>
-    <t>Identifiant de l’entrée</t>
+    <t>Identifiant</t>
   </si>
   <si>
     <t>FRLMEntry.header.identifier</t>
@@ -460,7 +460,7 @@
     <t>JDV-SOPClass_CISIS (1.2.250.1.213.1.1.5.689)</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-sop-class-cisis|20260716085851</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-sop-class-cisis|20260916095453</t>
   </si>
   <si>
     <t>FRLMSOPInstance.instanceNumber</t>

--- a/main/ig/StructureDefinition-FRLMSOPInstance.xlsx
+++ b/main/ig/StructureDefinition-FRLMSOPInstance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T20:10:21+00:00</t>
+    <t>2026-10-08T12:56:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
